--- a/docs/data/CoastalDroneMaps.xlsx
+++ b/docs/data/CoastalDroneMaps.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fer/Documents/PYTHON/11_coastalDroneMaps_github/raw_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fer/Documents/PYTHON/11_coastalDroneMaps_github/docs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8085B4-837D-A648-981B-43CE5B4FE825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55C5D5C-69B1-3941-9444-5A52B6F23A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38720" yWindow="820" windowWidth="38080" windowHeight="20780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2284" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2425" uniqueCount="521">
   <si>
     <t>GCP</t>
   </si>
@@ -100,9 +100,6 @@
     <t>RGB+MS</t>
   </si>
   <si>
-    <t>BIODIV</t>
-  </si>
-  <si>
     <t>TINAMAYOR</t>
   </si>
   <si>
@@ -1472,6 +1469,120 @@
   </si>
   <si>
     <t>comments</t>
+  </si>
+  <si>
+    <t>20250523_074700_NORGRASS25_GAL_NANO_18_50m</t>
+  </si>
+  <si>
+    <t>FERROL_MUGARDOS</t>
+  </si>
+  <si>
+    <t>POLYGON ((-8.264118511851736 43.45459039297884, -8.264118511851736 43.460705885199985, -8.271171779208803 43.460705885199985, -8.271171779208803 43.45459039297884, -8.264118511851736 43.45459039297884))</t>
+  </si>
+  <si>
+    <t>https://creativecommons.org/licenses/by/4.0/</t>
+  </si>
+  <si>
+    <t>2025-05-23T07:47:00</t>
+  </si>
+  <si>
+    <t>BIODIV (MITECO-IEO-CSIC)</t>
+  </si>
+  <si>
+    <t>Fernando Garcia-Gonzalez (GEAM IEO-CSIC)</t>
+  </si>
+  <si>
+    <t>https://filedn.eu/lxdSetOgU6G8FNMH4dxBDJQ/GEAM_GDB/2_DRONE/20250523_074700_NORGRASS25_GAL_NANO_18_50m.jpg</t>
+  </si>
+  <si>
+    <t>20250524_085100_NORGRASS25_GAL_NANO_19_12m</t>
+  </si>
+  <si>
+    <t>FERROL_MANIÑOS</t>
+  </si>
+  <si>
+    <t>POLYGON ((-8.200047753744158 43.460358482795286, -8.200047753744158 43.46159908508305, -8.201782741046124 43.46159908508305, -8.201782741046124 43.460358482795286, -8.200047753744158 43.460358482795286))</t>
+  </si>
+  <si>
+    <t>2025-05-24T08:51:00</t>
+  </si>
+  <si>
+    <t> 0.00973</t>
+  </si>
+  <si>
+    <t>https://filedn.eu/lxdSetOgU6G8FNMH4dxBDJQ/GEAM_GDB/2_DRONE/20250524_085100_NORGRASS25_GAL_NANO_19_12m.jpg</t>
+  </si>
+  <si>
+    <t>20250524_090900_NORGRASS25_GAL_NANO_19_50m</t>
+  </si>
+  <si>
+    <t>POLYGON ((-8.199168512228438 43.45929145095331, -8.199168512228438 43.46219613872979, -8.205465780813697 43.46219613872979, -8.205465780813697 43.45929145095331, -8.199168512228438 43.45929145095331))</t>
+  </si>
+  <si>
+    <t>2025-05-24T09:09:00</t>
+  </si>
+  <si>
+    <t>https://filedn.eu/lxdSetOgU6G8FNMH4dxBDJQ/GEAM_GDB/2_DRONE/20250524_090900_NORGRASS25_GAL_NANO_19_50m.jpg</t>
+  </si>
+  <si>
+    <t>20250524_201900_NORGRASS25_ARES1_25m</t>
+  </si>
+  <si>
+    <t>ARES_PUENTE</t>
+  </si>
+  <si>
+    <t>POLYGON ((-8.16288942400866 43.410981291159814, -8.16288942400866 43.41394785877393, -8.168714332424482 43.41394785877393, -8.168714332424482 43.410981291159814, -8.16288942400866 43.410981291159814))</t>
+  </si>
+  <si>
+    <t>2025-05-24T20:19:00</t>
+  </si>
+  <si>
+    <t>https://filedn.eu/lxdSetOgU6G8FNMH4dxBDJQ/GEAM_GDB/2_DRONE/20250524_201900_NORGRASS25_ARES1_25m.jpg</t>
+  </si>
+  <si>
+    <t>20250524_205200_NORGRASS25_ARES2_70m</t>
+  </si>
+  <si>
+    <t>ARES_CENTRO</t>
+  </si>
+  <si>
+    <t>POLYGON ((-8.15824770127373 43.40979206959821, -8.15824770127373 43.413312861033816, -8.166011493685506 43.413312861033816, -8.166011493685506 43.40979206959821, -8.15824770127373 43.40979206959821))</t>
+  </si>
+  <si>
+    <t>2025-05-24T20:52:00</t>
+  </si>
+  <si>
+    <t>https://filedn.eu/lxdSetOgU6G8FNMH4dxBDJQ/GEAM_GDB/2_DRONE/20250524_205200_NORGRASS25_ARES2_70m.jpg</t>
+  </si>
+  <si>
+    <t>20250524_211300_NORGRASS25_ARES3_50m</t>
+  </si>
+  <si>
+    <t>ARES_INTERIOR</t>
+  </si>
+  <si>
+    <t>POLYGON ((-8.154235789679465 43.41093038172673, -8.154235789679465 43.413518886878755, -8.157748150839826 43.413518886878755, -8.157748150839826 43.41093038172673, -8.154235789679465 43.41093038172673))</t>
+  </si>
+  <si>
+    <t>2025-05-24T21:13:00</t>
+  </si>
+  <si>
+    <t>https://filedn.eu/lxdSetOgU6G8FNMH4dxBDJQ/GEAM_GDB/2_DRONE/20250524_211300_NORGRASS25_ARES3_50m.jpg</t>
+  </si>
+  <si>
+    <t>20250525_210000_NORGRASS25_FERROL_NEDA_65m</t>
+  </si>
+  <si>
+    <t>FERROL_NEDA</t>
+  </si>
+  <si>
+    <t>POLYGON ((-8.162434029104807 43.488184263750284, -8.162434029104807 43.49834749721291, -8.171770406993076 43.49834749721291, -8.171770406993076 43.488184263750284, -8.162434029104807 43.488184263750284))</t>
+  </si>
+  <si>
+    <t>2025-05-25T21:00:00</t>
+  </si>
+  <si>
+    <t>https://filedn.eu/lxdSetOgU6G8FNMH4dxBDJQ/GEAM_GDB/2_DRONE/20250525_210000_NORGRASS25_FERROL_NEDA_65m.jpg</t>
   </si>
 </sst>
 </file>
@@ -1563,7 +1674,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1583,6 +1694,10 @@
     </xf>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1885,7 +2000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB1000"/>
+  <dimension ref="A1:AG1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="60.5" bestFit="1" customWidth="1"/>
@@ -1918,93 +2033,93 @@
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="L1" s="1" t="s">
+      <c r="O1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AB1" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
@@ -2022,16 +2137,16 @@
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>12</v>
@@ -2040,7 +2155,7 @@
         <v>11</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>5</v>
@@ -2058,7 +2173,7 @@
         <v>10</v>
       </c>
       <c r="S2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T2" s="2" t="s">
         <v>7</v>
@@ -2084,7 +2199,7 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>15</v>
@@ -2102,16 +2217,16 @@
         <v>3</v>
       </c>
       <c r="G3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>12</v>
@@ -2120,7 +2235,7 @@
         <v>11</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>5</v>
@@ -2138,7 +2253,7 @@
         <v>10</v>
       </c>
       <c r="S3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T3" s="2" t="s">
         <v>7</v>
@@ -2164,7 +2279,7 @@
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>17</v>
@@ -2182,16 +2297,16 @@
         <v>3</v>
       </c>
       <c r="G4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>1</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>12</v>
@@ -2200,7 +2315,7 @@
         <v>11</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>5</v>
@@ -2218,7 +2333,7 @@
         <v>10</v>
       </c>
       <c r="S4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T4" s="2" t="s">
         <v>7</v>
@@ -2244,7 +2359,7 @@
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>19</v>
@@ -2262,16 +2377,16 @@
         <v>3</v>
       </c>
       <c r="G5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>1</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>12</v>
@@ -2280,7 +2395,7 @@
         <v>11</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>5</v>
@@ -2298,7 +2413,7 @@
         <v>10</v>
       </c>
       <c r="S5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T5" s="2" t="s">
         <v>7</v>
@@ -2324,7 +2439,7 @@
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>23</v>
@@ -2342,7 +2457,7 @@
         <v>3</v>
       </c>
       <c r="G6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>20</v>
@@ -2351,16 +2466,16 @@
         <v>21</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>26</v>
+        <v>125</v>
+      </c>
+      <c r="K6" t="s">
+        <v>488</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>5</v>
@@ -2378,7 +2493,7 @@
         <v>10</v>
       </c>
       <c r="S6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T6" s="2" t="s">
         <v>25</v>
@@ -2407,10 +2522,10 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C7" s="2">
         <v>43.384662727310598</v>
@@ -2419,31 +2534,31 @@
         <v>-4.5123172298179197</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>26</v>
+        <v>125</v>
+      </c>
+      <c r="K7" t="s">
+        <v>488</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>5</v>
@@ -2461,7 +2576,7 @@
         <v>10</v>
       </c>
       <c r="S7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>25</v>
@@ -2490,10 +2605,10 @@
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="2">
         <v>43.513093712654801</v>
@@ -2502,31 +2617,31 @@
         <v>-5.3843911724636602</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>26</v>
+        <v>125</v>
+      </c>
+      <c r="K8" t="s">
+        <v>488</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>5</v>
@@ -2544,7 +2659,7 @@
         <v>10</v>
       </c>
       <c r="S8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T8" s="2" t="s">
         <v>25</v>
@@ -2573,10 +2688,10 @@
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" s="2">
         <v>43.524783315237997</v>
@@ -2585,31 +2700,31 @@
         <v>-5.38128701718255</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>26</v>
+        <v>125</v>
+      </c>
+      <c r="K9" t="s">
+        <v>488</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>5</v>
@@ -2627,7 +2742,7 @@
         <v>10</v>
       </c>
       <c r="S9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T9" s="2" t="s">
         <v>25</v>
@@ -2656,10 +2771,10 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="2">
         <v>43.433737009900199</v>
@@ -2668,31 +2783,31 @@
         <v>-4.8345613211630996</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>26</v>
+        <v>125</v>
+      </c>
+      <c r="K10" t="s">
+        <v>488</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>5</v>
@@ -2710,7 +2825,7 @@
         <v>10</v>
       </c>
       <c r="S10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T10" s="2" t="s">
         <v>25</v>
@@ -2736,10 +2851,10 @@
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C11" s="2">
         <v>43.434173202733298</v>
@@ -2748,31 +2863,31 @@
         <v>-4.8329391676358799</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>26</v>
+        <v>125</v>
+      </c>
+      <c r="K11" t="s">
+        <v>488</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>5</v>
@@ -2790,7 +2905,7 @@
         <v>10</v>
       </c>
       <c r="S11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T11" s="2" t="s">
         <v>25</v>
@@ -2819,10 +2934,10 @@
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" s="2">
         <v>43.396053001293197</v>
@@ -2831,31 +2946,31 @@
         <v>-4.6117341227206801</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>26</v>
+        <v>125</v>
+      </c>
+      <c r="K12" t="s">
+        <v>488</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>5</v>
@@ -2873,7 +2988,7 @@
         <v>10</v>
       </c>
       <c r="S12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T12" s="2" t="s">
         <v>25</v>
@@ -2902,10 +3017,10 @@
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" s="2">
         <v>43.434993118817701</v>
@@ -2914,31 +3029,31 @@
         <v>-4.8353968567567804</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>26</v>
+        <v>125</v>
+      </c>
+      <c r="K13" t="s">
+        <v>488</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>5</v>
@@ -2956,7 +3071,7 @@
         <v>10</v>
       </c>
       <c r="S13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T13" s="2" t="s">
         <v>7</v>
@@ -2985,10 +3100,10 @@
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" s="2">
         <v>43.523270379864599</v>
@@ -2997,31 +3112,31 @@
         <v>-5.3840309169518097</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>26</v>
+        <v>125</v>
+      </c>
+      <c r="K14" t="s">
+        <v>488</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>5</v>
@@ -3039,7 +3154,7 @@
         <v>10</v>
       </c>
       <c r="S14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T14" s="2" t="s">
         <v>25</v>
@@ -3068,10 +3183,10 @@
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" s="2">
         <v>43.5194007524181</v>
@@ -3080,31 +3195,31 @@
         <v>-5.3857666357548997</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>26</v>
+        <v>125</v>
+      </c>
+      <c r="K15" t="s">
+        <v>488</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>5</v>
@@ -3122,7 +3237,7 @@
         <v>10</v>
       </c>
       <c r="S15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T15" s="2" t="s">
         <v>25</v>
@@ -3151,10 +3266,10 @@
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" s="2">
         <v>43.503717443857603</v>
@@ -3163,31 +3278,31 @@
         <v>-5.4228774392088503</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>26</v>
+        <v>125</v>
+      </c>
+      <c r="K16" t="s">
+        <v>488</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>5</v>
@@ -3205,7 +3320,7 @@
         <v>10</v>
       </c>
       <c r="S16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T16" s="2" t="s">
         <v>7</v>
@@ -3234,10 +3349,10 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C17" s="2">
         <v>43.514891402549203</v>
@@ -3246,31 +3361,31 @@
         <v>-5.3913869277144899</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G17" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>26</v>
+        <v>125</v>
+      </c>
+      <c r="K17" t="s">
+        <v>488</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>5</v>
@@ -3288,7 +3403,7 @@
         <v>10</v>
       </c>
       <c r="S17" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T17" s="2" t="s">
         <v>7</v>
@@ -3317,10 +3432,10 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="2">
         <v>43.509361517338199</v>
@@ -3329,31 +3444,31 @@
         <v>-5.4048557942783297</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G18" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>26</v>
+        <v>125</v>
+      </c>
+      <c r="K18" t="s">
+        <v>488</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>5</v>
@@ -3371,7 +3486,7 @@
         <v>10</v>
       </c>
       <c r="S18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T18" s="2" t="s">
         <v>7</v>
@@ -3400,10 +3515,10 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C19" s="2">
         <v>43.506580933435401</v>
@@ -3412,31 +3527,31 @@
         <v>-5.4162426144645996</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G19" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>26</v>
+        <v>125</v>
+      </c>
+      <c r="K19" t="s">
+        <v>488</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>5</v>
@@ -3454,7 +3569,7 @@
         <v>10</v>
       </c>
       <c r="S19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T19" s="2" t="s">
         <v>7</v>
@@ -3483,10 +3598,10 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C20" s="2">
         <v>43.514349029946899</v>
@@ -3495,31 +3610,31 @@
         <v>-5.4049936421013003</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G20" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>26</v>
+        <v>125</v>
+      </c>
+      <c r="K20" t="s">
+        <v>488</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>5</v>
@@ -3537,7 +3652,7 @@
         <v>10</v>
       </c>
       <c r="S20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T20" s="2" t="s">
         <v>7</v>
@@ -3566,10 +3681,10 @@
     </row>
     <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C21" s="2">
         <v>43.521491628930796</v>
@@ -3578,31 +3693,31 @@
         <v>-5.3946647505433099</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G21" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>26</v>
+        <v>125</v>
+      </c>
+      <c r="K21" t="s">
+        <v>488</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>10</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>5</v>
@@ -3620,7 +3735,7 @@
         <v>10</v>
       </c>
       <c r="S21" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T21" s="2" t="s">
         <v>7</v>
@@ -3649,10 +3764,10 @@
     </row>
     <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C22" s="2">
         <v>43.532895054012997</v>
@@ -3661,31 +3776,31 @@
         <v>-5.3884896487231897</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>26</v>
+        <v>125</v>
+      </c>
+      <c r="K22" t="s">
+        <v>488</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>5</v>
@@ -3703,7 +3818,7 @@
         <v>10</v>
       </c>
       <c r="S22" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T22" s="2" t="s">
         <v>7</v>
@@ -3732,10 +3847,10 @@
     </row>
     <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C23" s="2">
         <v>43.512520764698699</v>
@@ -3744,31 +3859,31 @@
         <v>-5.4009372418816497</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G23" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>26</v>
+        <v>125</v>
+      </c>
+      <c r="K23" t="s">
+        <v>488</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>5</v>
@@ -3786,7 +3901,7 @@
         <v>10</v>
       </c>
       <c r="S23" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T23" s="2" t="s">
         <v>7</v>
@@ -3815,10 +3930,10 @@
     </row>
     <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C24" s="2">
         <v>43.518147439675303</v>
@@ -3827,31 +3942,31 @@
         <v>-5.3825743426355501</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G24" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>26</v>
+        <v>125</v>
+      </c>
+      <c r="K24" t="s">
+        <v>488</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>10</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>5</v>
@@ -3869,7 +3984,7 @@
         <v>10</v>
       </c>
       <c r="S24" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T24" s="2" t="s">
         <v>7</v>
@@ -3898,10 +4013,10 @@
     </row>
     <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C25" s="2">
         <v>43.522282170161297</v>
@@ -3910,31 +4025,31 @@
         <v>-5.3868113029432898</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G25" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>26</v>
+        <v>125</v>
+      </c>
+      <c r="K25" t="s">
+        <v>488</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>5</v>
@@ -3952,7 +4067,7 @@
         <v>10</v>
       </c>
       <c r="S25" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T25" s="2" t="s">
         <v>7</v>
@@ -3981,10 +4096,10 @@
     </row>
     <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C26" s="2">
         <v>43.411216784476601</v>
@@ -3993,31 +4108,31 @@
         <v>-3.45635504550257</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J26" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K26" t="s">
+        <v>488</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M26" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>5</v>
@@ -4035,7 +4150,7 @@
         <v>10</v>
       </c>
       <c r="S26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T26" s="2" t="s">
         <v>7</v>
@@ -4061,10 +4176,10 @@
     </row>
     <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C27" s="2">
         <v>43.438201701304898</v>
@@ -4073,31 +4188,31 @@
         <v>-3.47094471704174</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G27" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J27" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K27" t="s">
+        <v>488</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M27" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>5</v>
@@ -4115,7 +4230,7 @@
         <v>10</v>
       </c>
       <c r="S27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T27" s="2" t="s">
         <v>7</v>
@@ -4141,10 +4256,10 @@
     </row>
     <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C28" s="2">
         <v>43.437798688429901</v>
@@ -4153,31 +4268,31 @@
         <v>-3.4674037124083998</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G28" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J28" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K28" t="s">
+        <v>488</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M28" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>5</v>
@@ -4195,7 +4310,7 @@
         <v>10</v>
       </c>
       <c r="S28" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T28" s="2" t="s">
         <v>7</v>
@@ -4221,10 +4336,10 @@
     </row>
     <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C29" s="2">
         <v>43.4208757398766</v>
@@ -4233,31 +4348,31 @@
         <v>-3.47828529185673</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G29" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J29" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K29" t="s">
+        <v>488</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M29" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>5</v>
@@ -4275,7 +4390,7 @@
         <v>10</v>
       </c>
       <c r="S29" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T29" s="2" t="s">
         <v>7</v>
@@ -4301,10 +4416,10 @@
     </row>
     <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C30" s="2">
         <v>43.406367086835701</v>
@@ -4313,31 +4428,31 @@
         <v>-3.4584905847101899</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G30" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J30" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K30" t="s">
+        <v>488</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M30" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>5</v>
@@ -4355,7 +4470,7 @@
         <v>10</v>
       </c>
       <c r="S30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T30" s="2" t="s">
         <v>7</v>
@@ -4381,10 +4496,10 @@
     </row>
     <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C31" s="2">
         <v>43.516198882299399</v>
@@ -4393,31 +4508,31 @@
         <v>-5.3979510779888802</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G31" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J31" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K31" t="s">
+        <v>488</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M31" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>5</v>
@@ -4435,7 +4550,7 @@
         <v>10</v>
       </c>
       <c r="S31" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T31" s="2" t="s">
         <v>7</v>
@@ -4461,10 +4576,10 @@
     </row>
     <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C32" s="2">
         <v>43.525775332313799</v>
@@ -4473,31 +4588,31 @@
         <v>-7.0186722519353202</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G32" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J32" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K32" t="s">
+        <v>488</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M32" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>5</v>
@@ -4515,7 +4630,7 @@
         <v>10</v>
       </c>
       <c r="S32" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T32" s="2" t="s">
         <v>7</v>
@@ -4541,10 +4656,10 @@
     </row>
     <row r="33" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C33" s="2">
         <v>43.527534669747503</v>
@@ -4553,31 +4668,31 @@
         <v>-7.0193026771607103</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G33" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J33" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K33" t="s">
+        <v>488</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M33" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>5</v>
@@ -4595,7 +4710,7 @@
         <v>10</v>
       </c>
       <c r="S33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T33" s="2" t="s">
         <v>25</v>
@@ -4621,10 +4736,10 @@
     </row>
     <row r="34" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C34" s="2">
         <v>43.711671680935197</v>
@@ -4633,31 +4748,31 @@
         <v>-7.8665303556387602</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G34" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J34" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K34" t="s">
+        <v>488</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M34" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>5</v>
@@ -4675,7 +4790,7 @@
         <v>10</v>
       </c>
       <c r="S34" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T34" s="2" t="s">
         <v>7</v>
@@ -4701,10 +4816,10 @@
     </row>
     <row r="35" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C35" s="2">
         <v>43.712598946707502</v>
@@ -4713,31 +4828,31 @@
         <v>-7.8672858569733002</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G35" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J35" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K35" t="s">
+        <v>488</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M35" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>5</v>
@@ -4755,7 +4870,7 @@
         <v>10</v>
       </c>
       <c r="S35" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T35" s="2" t="s">
         <v>7</v>
@@ -4781,10 +4896,10 @@
     </row>
     <row r="36" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C36" s="2">
         <v>43.704005642936302</v>
@@ -4793,31 +4908,31 @@
         <v>-7.8752594956175903</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G36" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J36" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K36" t="s">
+        <v>488</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M36" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="N36" s="2" t="s">
         <v>5</v>
@@ -4835,7 +4950,7 @@
         <v>10</v>
       </c>
       <c r="S36" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T36" s="2" t="s">
         <v>7</v>
@@ -4861,10 +4976,10 @@
     </row>
     <row r="37" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C37" s="2">
         <v>43.698429786618298</v>
@@ -4873,31 +4988,31 @@
         <v>-7.8769243358526797</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G37" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J37" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K37" t="s">
+        <v>488</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M37" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M37" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>5</v>
@@ -4915,7 +5030,7 @@
         <v>10</v>
       </c>
       <c r="S37" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T37" s="2" t="s">
         <v>7</v>
@@ -4941,10 +5056,10 @@
     </row>
     <row r="38" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C38" s="2">
         <v>43.713458798067499</v>
@@ -4953,31 +5068,31 @@
         <v>-7.6974186941587801</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J38" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K38" t="s">
+        <v>488</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M38" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>5</v>
@@ -4992,10 +5107,10 @@
         <v>14.3</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S38" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>7</v>
@@ -5021,10 +5136,10 @@
     </row>
     <row r="39" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C39" s="2">
         <v>43.711909895868303</v>
@@ -5033,31 +5148,31 @@
         <v>-7.6963090640861802</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G39" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J39" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K39" t="s">
+        <v>488</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M39" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>5</v>
@@ -5072,10 +5187,10 @@
         <v>105</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S39" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T39" s="2" t="s">
         <v>7</v>
@@ -5101,10 +5216,10 @@
     </row>
     <row r="40" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C40" s="2">
         <v>43.735616599706297</v>
@@ -5113,31 +5228,31 @@
         <v>-7.6762260473486696</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G40" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J40" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K40" t="s">
+        <v>488</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M40" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>5</v>
@@ -5155,7 +5270,7 @@
         <v>10</v>
       </c>
       <c r="S40" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T40" s="2" t="s">
         <v>7</v>
@@ -5181,10 +5296,10 @@
     </row>
     <row r="41" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C41" s="2">
         <v>43.736062862386298</v>
@@ -5193,31 +5308,31 @@
         <v>-7.6740555083839999</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G41" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J41" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K41" t="s">
+        <v>488</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M41" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>5</v>
@@ -5232,10 +5347,10 @@
         <v>23.1</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S41" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T41" s="2" t="s">
         <v>7</v>
@@ -5261,7 +5376,7 @@
     </row>
     <row r="42" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B42" s="5">
         <v>43101</v>
@@ -5273,43 +5388,43 @@
         <v>2.8017500000000002</v>
       </c>
       <c r="E42" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F42" t="s">
         <v>3</v>
       </c>
       <c r="G42" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H42" t="s">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J42" t="s">
+        <v>211</v>
+      </c>
+      <c r="K42" t="s">
         <v>212</v>
       </c>
-      <c r="K42" t="s">
+      <c r="L42" t="s">
         <v>213</v>
       </c>
-      <c r="L42" t="s">
-        <v>214</v>
-      </c>
       <c r="M42" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N42" t="s">
         <v>5</v>
       </c>
       <c r="O42" t="s">
+        <v>215</v>
+      </c>
+      <c r="P42" t="s">
+        <v>217</v>
+      </c>
+      <c r="R42" t="s">
         <v>216</v>
-      </c>
-      <c r="P42" t="s">
-        <v>218</v>
-      </c>
-      <c r="R42" t="s">
-        <v>217</v>
       </c>
       <c r="T42" t="s">
         <v>7</v>
@@ -5324,12 +5439,12 @@
         <v>9</v>
       </c>
       <c r="AB42" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="43" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B43" s="5">
         <v>43101</v>
@@ -5341,43 +5456,43 @@
         <v>3.295839</v>
       </c>
       <c r="E43" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F43" t="s">
         <v>3</v>
       </c>
       <c r="G43" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H43" t="s">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J43" t="s">
+        <v>211</v>
+      </c>
+      <c r="K43" t="s">
         <v>212</v>
       </c>
-      <c r="K43" t="s">
-        <v>213</v>
-      </c>
       <c r="L43" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M43" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N43" t="s">
         <v>5</v>
       </c>
       <c r="O43" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P43" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R43" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="T43" t="s">
         <v>7</v>
@@ -5392,12 +5507,12 @@
         <v>9</v>
       </c>
       <c r="AB43" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="44" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B44" s="5">
         <v>43670</v>
@@ -5409,46 +5524,46 @@
         <v>2.8166069999999999</v>
       </c>
       <c r="E44" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F44" t="s">
         <v>3</v>
       </c>
       <c r="G44" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H44" t="s">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J44" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K44" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L44" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N44" t="s">
         <v>5</v>
       </c>
       <c r="O44" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P44" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R44" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S44" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="T44" t="s">
         <v>7</v>
@@ -5463,12 +5578,12 @@
         <v>9</v>
       </c>
       <c r="AB44" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="45" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B45" s="5">
         <v>43749</v>
@@ -5480,46 +5595,46 @@
         <v>2.8164820000000002</v>
       </c>
       <c r="E45" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F45" t="s">
         <v>3</v>
       </c>
       <c r="G45" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H45" t="s">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J45" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K45" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L45" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M45" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N45" t="s">
         <v>5</v>
       </c>
       <c r="O45" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P45" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R45" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S45" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="T45" t="s">
         <v>7</v>
@@ -5534,12 +5649,12 @@
         <v>9</v>
       </c>
       <c r="AB45" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="46" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B46" s="5">
         <v>44104</v>
@@ -5551,46 +5666,46 @@
         <v>2.8160590000000001</v>
       </c>
       <c r="E46" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F46" t="s">
         <v>3</v>
       </c>
       <c r="G46" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H46" t="s">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J46" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K46" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L46" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M46" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N46" t="s">
         <v>5</v>
       </c>
       <c r="O46" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P46" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R46" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S46" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="T46" t="s">
         <v>7</v>
@@ -5605,12 +5720,12 @@
         <v>9</v>
       </c>
       <c r="AB46" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="47" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B47" s="5">
         <v>44223</v>
@@ -5622,43 +5737,43 @@
         <v>2.4710519999999998</v>
       </c>
       <c r="E47" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F47" t="s">
         <v>3</v>
       </c>
       <c r="G47" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H47" t="s">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J47" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K47" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L47" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M47" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N47" t="s">
         <v>5</v>
       </c>
       <c r="O47" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P47" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R47" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="T47" t="s">
         <v>7</v>
@@ -5673,12 +5788,12 @@
         <v>9</v>
       </c>
       <c r="AB47" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="48" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B48" s="5">
         <v>44308</v>
@@ -5690,46 +5805,46 @@
         <v>3.1689720000000001</v>
       </c>
       <c r="E48" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F48" t="s">
         <v>3</v>
       </c>
       <c r="G48" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H48" t="s">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J48" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K48" t="s">
+        <v>237</v>
+      </c>
+      <c r="L48" t="s">
         <v>238</v>
       </c>
-      <c r="L48" t="s">
-        <v>239</v>
-      </c>
       <c r="M48" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N48" t="s">
         <v>5</v>
       </c>
       <c r="O48" t="s">
+        <v>239</v>
+      </c>
+      <c r="P48" t="s">
+        <v>217</v>
+      </c>
+      <c r="R48" t="s">
+        <v>221</v>
+      </c>
+      <c r="S48" t="s">
         <v>240</v>
-      </c>
-      <c r="P48" t="s">
-        <v>218</v>
-      </c>
-      <c r="R48" t="s">
-        <v>222</v>
-      </c>
-      <c r="S48" t="s">
-        <v>241</v>
       </c>
       <c r="T48" t="s">
         <v>7</v>
@@ -5744,12 +5859,12 @@
         <v>9</v>
       </c>
       <c r="AB48" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="49" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B49" s="5">
         <v>44315</v>
@@ -5761,43 +5876,43 @@
         <v>3.1440030000000001</v>
       </c>
       <c r="E49" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F49" t="s">
         <v>3</v>
       </c>
       <c r="G49" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H49" t="s">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J49" t="s">
+        <v>211</v>
+      </c>
+      <c r="K49" t="s">
         <v>212</v>
       </c>
-      <c r="K49" t="s">
-        <v>213</v>
-      </c>
       <c r="L49" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M49" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N49" t="s">
         <v>5</v>
       </c>
       <c r="O49" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P49" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R49" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="T49" t="s">
         <v>7</v>
@@ -5812,12 +5927,12 @@
         <v>9</v>
       </c>
       <c r="AB49" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="50" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B50" s="5">
         <v>44316</v>
@@ -5829,46 +5944,46 @@
         <v>3.2280069999999998</v>
       </c>
       <c r="E50" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F50" t="s">
         <v>3</v>
       </c>
       <c r="G50" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H50" t="s">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J50" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K50" t="s">
+        <v>237</v>
+      </c>
+      <c r="L50" t="s">
         <v>238</v>
       </c>
-      <c r="L50" t="s">
-        <v>239</v>
-      </c>
       <c r="M50" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N50" t="s">
         <v>5</v>
       </c>
       <c r="O50" t="s">
+        <v>239</v>
+      </c>
+      <c r="P50" t="s">
+        <v>217</v>
+      </c>
+      <c r="R50" t="s">
+        <v>247</v>
+      </c>
+      <c r="S50" t="s">
         <v>240</v>
-      </c>
-      <c r="P50" t="s">
-        <v>218</v>
-      </c>
-      <c r="R50" t="s">
-        <v>248</v>
-      </c>
-      <c r="S50" t="s">
-        <v>241</v>
       </c>
       <c r="T50" t="s">
         <v>7</v>
@@ -5883,12 +5998,12 @@
         <v>9</v>
       </c>
       <c r="AB50" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="51" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B51" s="5">
         <v>44392</v>
@@ -5900,46 +6015,46 @@
         <v>3.2933560000000002</v>
       </c>
       <c r="E51" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F51" t="s">
         <v>3</v>
       </c>
       <c r="G51" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H51" t="s">
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J51" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K51" t="s">
+        <v>251</v>
+      </c>
+      <c r="L51" t="s">
         <v>252</v>
       </c>
-      <c r="L51" t="s">
-        <v>253</v>
-      </c>
       <c r="M51" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N51" t="s">
         <v>5</v>
       </c>
       <c r="O51" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P51" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R51" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S51" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T51" t="s">
         <v>7</v>
@@ -5954,12 +6069,12 @@
         <v>9</v>
       </c>
       <c r="AB51" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="52" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B52" s="5">
         <v>44419</v>
@@ -5971,46 +6086,46 @@
         <v>3.2299410000000002</v>
       </c>
       <c r="E52" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F52" t="s">
         <v>3</v>
       </c>
       <c r="G52" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H52" t="s">
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J52" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K52" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L52" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="M52" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N52" t="s">
         <v>5</v>
       </c>
       <c r="O52" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P52" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R52" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S52" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T52" t="s">
         <v>7</v>
@@ -6025,12 +6140,12 @@
         <v>9</v>
       </c>
       <c r="AB52" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="53" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B53" s="5">
         <v>44419</v>
@@ -6042,46 +6157,46 @@
         <v>3.2299410000000002</v>
       </c>
       <c r="E53" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F53" t="s">
         <v>3</v>
       </c>
       <c r="G53" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H53" t="s">
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J53" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K53" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L53" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="M53" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N53" t="s">
         <v>5</v>
       </c>
       <c r="O53" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P53" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R53" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S53" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T53" t="s">
         <v>7</v>
@@ -6096,12 +6211,12 @@
         <v>9</v>
       </c>
       <c r="AB53" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="54" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B54" s="5">
         <v>44488</v>
@@ -6113,46 +6228,46 @@
         <v>2.8160980000000002</v>
       </c>
       <c r="E54" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F54" t="s">
         <v>3</v>
       </c>
       <c r="G54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H54" t="s">
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J54" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K54" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L54" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N54" t="s">
         <v>5</v>
       </c>
       <c r="O54" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P54" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R54" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="S54" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="T54" t="s">
         <v>7</v>
@@ -6167,12 +6282,12 @@
         <v>9</v>
       </c>
       <c r="AB54" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="55" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B55" s="5">
         <v>44488</v>
@@ -6184,46 +6299,46 @@
         <v>2.8167209999999998</v>
       </c>
       <c r="E55" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F55" t="s">
         <v>3</v>
       </c>
       <c r="G55" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H55" t="s">
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J55" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K55" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L55" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M55" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N55" t="s">
         <v>5</v>
       </c>
       <c r="O55" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P55" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R55" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="S55" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="T55" t="s">
         <v>7</v>
@@ -6238,12 +6353,12 @@
         <v>9</v>
       </c>
       <c r="AB55" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="56" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B56" s="5">
         <v>44497</v>
@@ -6255,46 +6370,46 @@
         <v>4.1825400000000004</v>
       </c>
       <c r="E56" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F56" t="s">
         <v>3</v>
       </c>
       <c r="G56" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H56" t="s">
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J56" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K56" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L56" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="M56" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N56" t="s">
         <v>5</v>
       </c>
       <c r="O56" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P56" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R56" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S56" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T56" t="s">
         <v>7</v>
@@ -6309,12 +6424,12 @@
         <v>9</v>
       </c>
       <c r="AB56" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="57" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B57" s="5">
         <v>44497</v>
@@ -6326,46 +6441,46 @@
         <v>4.2894220000000001</v>
       </c>
       <c r="E57" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F57" t="s">
         <v>3</v>
       </c>
       <c r="G57" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H57" t="s">
         <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J57" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K57" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L57" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="M57" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N57" t="s">
         <v>5</v>
       </c>
       <c r="O57" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P57" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R57" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S57" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T57" t="s">
         <v>7</v>
@@ -6380,12 +6495,12 @@
         <v>9</v>
       </c>
       <c r="AB57" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="58" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B58" s="5">
         <v>44497</v>
@@ -6397,46 +6512,46 @@
         <v>4.1029299999999997</v>
       </c>
       <c r="E58" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F58" t="s">
         <v>3</v>
       </c>
       <c r="G58" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H58" t="s">
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J58" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K58" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L58" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="M58" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N58" t="s">
         <v>5</v>
       </c>
       <c r="O58" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P58" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R58" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S58" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T58" t="s">
         <v>7</v>
@@ -6451,12 +6566,12 @@
         <v>9</v>
       </c>
       <c r="AB58" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="59" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B59" s="5">
         <v>44497</v>
@@ -6468,46 +6583,46 @@
         <v>4.0903109999999998</v>
       </c>
       <c r="E59" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F59" t="s">
         <v>3</v>
       </c>
       <c r="G59" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H59" t="s">
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J59" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K59" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L59" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="M59" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N59" t="s">
         <v>5</v>
       </c>
       <c r="O59" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P59" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R59" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S59" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T59" t="s">
         <v>7</v>
@@ -6522,12 +6637,12 @@
         <v>9</v>
       </c>
       <c r="AB59" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="60" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B60" s="5">
         <v>44521</v>
@@ -6539,46 +6654,46 @@
         <v>2.8084099999999999</v>
       </c>
       <c r="E60" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F60" t="s">
         <v>3</v>
       </c>
       <c r="G60" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H60" t="s">
         <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J60" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K60" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L60" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M60" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N60" t="s">
         <v>5</v>
       </c>
       <c r="O60" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P60" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R60" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="S60" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="T60" t="s">
         <v>7</v>
@@ -6593,12 +6708,12 @@
         <v>9</v>
       </c>
       <c r="AB60" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="61" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B61" s="5">
         <v>44522</v>
@@ -6610,46 +6725,46 @@
         <v>2.8017089999999998</v>
       </c>
       <c r="E61" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F61" t="s">
         <v>3</v>
       </c>
       <c r="G61" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H61" t="s">
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J61" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K61" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L61" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N61" t="s">
         <v>5</v>
       </c>
       <c r="O61" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P61" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R61" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="S61" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="T61" t="s">
         <v>7</v>
@@ -6664,12 +6779,12 @@
         <v>9</v>
       </c>
       <c r="AB61" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="62" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B62" s="5">
         <v>44523</v>
@@ -6681,46 +6796,46 @@
         <v>2.8033320000000002</v>
       </c>
       <c r="E62" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F62" t="s">
         <v>3</v>
       </c>
       <c r="G62" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H62" t="s">
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J62" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K62" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L62" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M62" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N62" t="s">
         <v>5</v>
       </c>
       <c r="O62" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P62" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R62" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="S62" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="T62" t="s">
         <v>7</v>
@@ -6735,12 +6850,12 @@
         <v>9</v>
       </c>
       <c r="AB62" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="63" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B63" s="5">
         <v>44523</v>
@@ -6752,46 +6867,46 @@
         <v>2.7920219999999998</v>
       </c>
       <c r="E63" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F63" t="s">
         <v>3</v>
       </c>
       <c r="G63" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H63" t="s">
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J63" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K63" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L63" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M63" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N63" t="s">
         <v>5</v>
       </c>
       <c r="O63" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P63" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R63" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="S63" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="T63" t="s">
         <v>7</v>
@@ -6806,12 +6921,12 @@
         <v>9</v>
       </c>
       <c r="AB63" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="64" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B64" s="5">
         <v>44543</v>
@@ -6823,46 +6938,46 @@
         <v>2.9541339999999998</v>
       </c>
       <c r="E64" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F64" t="s">
         <v>3</v>
       </c>
       <c r="G64" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H64" t="s">
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J64" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K64" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L64" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M64" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N64" t="s">
         <v>5</v>
       </c>
       <c r="O64" t="s">
+        <v>239</v>
+      </c>
+      <c r="P64" t="s">
+        <v>217</v>
+      </c>
+      <c r="R64" t="s">
+        <v>247</v>
+      </c>
+      <c r="S64" t="s">
         <v>240</v>
-      </c>
-      <c r="P64" t="s">
-        <v>218</v>
-      </c>
-      <c r="R64" t="s">
-        <v>248</v>
-      </c>
-      <c r="S64" t="s">
-        <v>241</v>
       </c>
       <c r="T64" t="s">
         <v>7</v>
@@ -6877,12 +6992,12 @@
         <v>9</v>
       </c>
       <c r="AB64" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="65" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B65" s="5">
         <v>44544</v>
@@ -6894,40 +7009,40 @@
         <v>2.8274110000000001</v>
       </c>
       <c r="E65" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F65" t="s">
         <v>3</v>
       </c>
       <c r="G65" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H65" t="s">
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J65" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L65" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="M65" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N65" t="s">
         <v>5</v>
       </c>
       <c r="O65" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P65" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R65" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T65" t="s">
         <v>7</v>
@@ -6942,12 +7057,12 @@
         <v>9</v>
       </c>
       <c r="AB65" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="66" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B66" s="5">
         <v>44545</v>
@@ -6959,40 +7074,40 @@
         <v>2.859515</v>
       </c>
       <c r="E66" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F66" t="s">
         <v>3</v>
       </c>
       <c r="G66" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H66" t="s">
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J66" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L66" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="M66" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N66" t="s">
         <v>5</v>
       </c>
       <c r="O66" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P66" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R66" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T66" t="s">
         <v>7</v>
@@ -7007,12 +7122,12 @@
         <v>9</v>
       </c>
       <c r="AB66" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="67" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B67" s="5">
         <v>44546</v>
@@ -7024,46 +7139,46 @@
         <v>3.2163249999999999</v>
       </c>
       <c r="E67" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F67" t="s">
         <v>3</v>
       </c>
       <c r="G67" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H67" t="s">
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J67" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K67" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L67" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M67" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N67" t="s">
         <v>5</v>
       </c>
       <c r="O67" t="s">
+        <v>239</v>
+      </c>
+      <c r="P67" t="s">
+        <v>217</v>
+      </c>
+      <c r="R67" t="s">
+        <v>247</v>
+      </c>
+      <c r="S67" t="s">
         <v>240</v>
-      </c>
-      <c r="P67" t="s">
-        <v>218</v>
-      </c>
-      <c r="R67" t="s">
-        <v>248</v>
-      </c>
-      <c r="S67" t="s">
-        <v>241</v>
       </c>
       <c r="T67" t="s">
         <v>7</v>
@@ -7078,12 +7193,12 @@
         <v>9</v>
       </c>
       <c r="AB67" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="68" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B68" s="5">
         <v>44546</v>
@@ -7095,40 +7210,40 @@
         <v>2.8281610000000001</v>
       </c>
       <c r="E68" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F68" t="s">
         <v>3</v>
       </c>
       <c r="G68" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H68" t="s">
         <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J68" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L68" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="M68" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N68" t="s">
         <v>5</v>
       </c>
       <c r="O68" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P68" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R68" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T68" t="s">
         <v>7</v>
@@ -7143,12 +7258,12 @@
         <v>9</v>
       </c>
       <c r="AB68" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="69" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B69" s="5">
         <v>44547</v>
@@ -7160,46 +7275,46 @@
         <v>3.3116629999999998</v>
       </c>
       <c r="E69" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F69" t="s">
         <v>3</v>
       </c>
       <c r="G69" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H69" t="s">
         <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J69" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K69" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L69" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M69" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N69" t="s">
         <v>5</v>
       </c>
       <c r="O69" t="s">
+        <v>239</v>
+      </c>
+      <c r="P69" t="s">
+        <v>217</v>
+      </c>
+      <c r="R69" t="s">
+        <v>247</v>
+      </c>
+      <c r="S69" t="s">
         <v>240</v>
-      </c>
-      <c r="P69" t="s">
-        <v>218</v>
-      </c>
-      <c r="R69" t="s">
-        <v>248</v>
-      </c>
-      <c r="S69" t="s">
-        <v>241</v>
       </c>
       <c r="T69" t="s">
         <v>7</v>
@@ -7214,12 +7329,12 @@
         <v>9</v>
       </c>
       <c r="AB69" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B70" s="5">
         <v>44547</v>
@@ -7231,46 +7346,46 @@
         <v>3.226216</v>
       </c>
       <c r="E70" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F70" t="s">
         <v>3</v>
       </c>
       <c r="G70" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H70" t="s">
         <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J70" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K70" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L70" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M70" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N70" t="s">
         <v>5</v>
       </c>
       <c r="O70" t="s">
+        <v>239</v>
+      </c>
+      <c r="P70" t="s">
+        <v>217</v>
+      </c>
+      <c r="R70" t="s">
+        <v>221</v>
+      </c>
+      <c r="S70" t="s">
         <v>240</v>
-      </c>
-      <c r="P70" t="s">
-        <v>218</v>
-      </c>
-      <c r="R70" t="s">
-        <v>222</v>
-      </c>
-      <c r="S70" t="s">
-        <v>241</v>
       </c>
       <c r="T70" t="s">
         <v>7</v>
@@ -7285,12 +7400,12 @@
         <v>9</v>
       </c>
       <c r="AB70" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="71" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B71" s="5">
         <v>44548</v>
@@ -7302,40 +7417,40 @@
         <v>2.883597</v>
       </c>
       <c r="E71" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F71" t="s">
         <v>3</v>
       </c>
       <c r="G71" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H71" t="s">
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J71" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L71" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="M71" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N71" t="s">
         <v>5</v>
       </c>
       <c r="O71" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P71" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R71" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T71" t="s">
         <v>7</v>
@@ -7350,12 +7465,12 @@
         <v>9</v>
       </c>
       <c r="AB71" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="72" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B72" s="5">
         <v>44550</v>
@@ -7367,40 +7482,40 @@
         <v>2.8592270000000002</v>
       </c>
       <c r="E72" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F72" t="s">
         <v>3</v>
       </c>
       <c r="G72" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H72" t="s">
         <v>1</v>
       </c>
       <c r="I72" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J72" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L72" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="M72" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N72" t="s">
         <v>5</v>
       </c>
       <c r="O72" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P72" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R72" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T72" t="s">
         <v>7</v>
@@ -7415,12 +7530,12 @@
         <v>9</v>
       </c>
       <c r="AB72" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="73" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B73" s="5">
         <v>44563</v>
@@ -7432,43 +7547,43 @@
         <v>2.3820160000000001</v>
       </c>
       <c r="E73" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F73" t="s">
         <v>3</v>
       </c>
       <c r="G73" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H73" t="s">
         <v>1</v>
       </c>
       <c r="I73" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J73" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L73" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M73" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N73" t="s">
         <v>5</v>
       </c>
       <c r="O73" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P73" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R73" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S73" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="T73" t="s">
         <v>7</v>
@@ -7483,12 +7598,12 @@
         <v>9</v>
       </c>
       <c r="AB73" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="74" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B74" s="5">
         <v>44608</v>
@@ -7500,46 +7615,46 @@
         <v>3.1936100000000001</v>
       </c>
       <c r="E74" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F74" t="s">
         <v>3</v>
       </c>
       <c r="G74" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H74" t="s">
         <v>1</v>
       </c>
       <c r="I74" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J74" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K74" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L74" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="M74" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N74" t="s">
         <v>5</v>
       </c>
       <c r="O74" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P74" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R74" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S74" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T74" t="s">
         <v>7</v>
@@ -7554,12 +7669,12 @@
         <v>9</v>
       </c>
       <c r="AB74" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="75" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B75" s="5">
         <v>44672</v>
@@ -7571,46 +7686,46 @@
         <v>4.2012280000000004</v>
       </c>
       <c r="E75" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F75" t="s">
         <v>3</v>
       </c>
       <c r="G75" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H75" t="s">
         <v>1</v>
       </c>
       <c r="I75" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J75" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K75" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L75" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="M75" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N75" t="s">
         <v>5</v>
       </c>
       <c r="O75" t="s">
+        <v>215</v>
+      </c>
+      <c r="P75" t="s">
+        <v>217</v>
+      </c>
+      <c r="R75" t="s">
         <v>216</v>
       </c>
-      <c r="P75" t="s">
-        <v>218</v>
-      </c>
-      <c r="R75" t="s">
-        <v>217</v>
-      </c>
       <c r="S75" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T75" t="s">
         <v>7</v>
@@ -7625,12 +7740,12 @@
         <v>9</v>
       </c>
       <c r="AB75" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="76" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B76" s="5">
         <v>44673</v>
@@ -7642,46 +7757,46 @@
         <v>4.2775939999999997</v>
       </c>
       <c r="E76" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F76" t="s">
         <v>3</v>
       </c>
       <c r="G76" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H76" t="s">
         <v>1</v>
       </c>
       <c r="I76" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J76" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K76" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L76" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="M76" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N76" t="s">
         <v>5</v>
       </c>
       <c r="O76" t="s">
+        <v>215</v>
+      </c>
+      <c r="P76" t="s">
+        <v>217</v>
+      </c>
+      <c r="R76" t="s">
         <v>216</v>
       </c>
-      <c r="P76" t="s">
-        <v>218</v>
-      </c>
-      <c r="R76" t="s">
-        <v>217</v>
-      </c>
       <c r="S76" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T76" t="s">
         <v>7</v>
@@ -7696,12 +7811,12 @@
         <v>9</v>
       </c>
       <c r="AB76" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="77" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B77" s="5">
         <v>44673</v>
@@ -7713,46 +7828,46 @@
         <v>4.0905550000000002</v>
       </c>
       <c r="E77" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F77" t="s">
         <v>3</v>
       </c>
       <c r="G77" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H77" t="s">
         <v>1</v>
       </c>
       <c r="I77" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J77" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K77" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L77" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="M77" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N77" t="s">
         <v>5</v>
       </c>
       <c r="O77" t="s">
+        <v>215</v>
+      </c>
+      <c r="P77" t="s">
+        <v>217</v>
+      </c>
+      <c r="R77" t="s">
         <v>216</v>
       </c>
-      <c r="P77" t="s">
-        <v>218</v>
-      </c>
-      <c r="R77" t="s">
-        <v>217</v>
-      </c>
       <c r="S77" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T77" t="s">
         <v>7</v>
@@ -7767,12 +7882,12 @@
         <v>9</v>
       </c>
       <c r="AB77" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="78" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B78" s="5">
         <v>44675</v>
@@ -7784,40 +7899,40 @@
         <v>4.3078440000000002</v>
       </c>
       <c r="E78" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F78" t="s">
         <v>3</v>
       </c>
       <c r="G78" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H78" t="s">
         <v>1</v>
       </c>
       <c r="I78" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J78" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L78" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M78" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N78" t="s">
         <v>5</v>
       </c>
       <c r="O78" t="s">
+        <v>215</v>
+      </c>
+      <c r="P78" t="s">
+        <v>217</v>
+      </c>
+      <c r="R78" t="s">
         <v>216</v>
-      </c>
-      <c r="P78" t="s">
-        <v>218</v>
-      </c>
-      <c r="R78" t="s">
-        <v>217</v>
       </c>
       <c r="T78" t="s">
         <v>7</v>
@@ -7832,12 +7947,12 @@
         <v>9</v>
       </c>
       <c r="AB78" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="79" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B79" s="5">
         <v>44675</v>
@@ -7849,40 +7964,40 @@
         <v>4.3085279999999999</v>
       </c>
       <c r="E79" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F79" t="s">
         <v>3</v>
       </c>
       <c r="G79" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H79" t="s">
         <v>1</v>
       </c>
       <c r="I79" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J79" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L79" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M79" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N79" t="s">
         <v>5</v>
       </c>
       <c r="O79" t="s">
+        <v>215</v>
+      </c>
+      <c r="P79" t="s">
+        <v>217</v>
+      </c>
+      <c r="R79" t="s">
         <v>216</v>
-      </c>
-      <c r="P79" t="s">
-        <v>218</v>
-      </c>
-      <c r="R79" t="s">
-        <v>217</v>
       </c>
       <c r="T79" t="s">
         <v>7</v>
@@ -7897,12 +8012,12 @@
         <v>9</v>
       </c>
       <c r="AB79" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="80" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B80" s="5">
         <v>44675</v>
@@ -7914,40 +8029,40 @@
         <v>4.3090320000000002</v>
       </c>
       <c r="E80" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F80" t="s">
         <v>3</v>
       </c>
       <c r="G80" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H80" t="s">
         <v>1</v>
       </c>
       <c r="I80" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J80" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L80" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M80" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N80" t="s">
         <v>5</v>
       </c>
       <c r="O80" t="s">
+        <v>215</v>
+      </c>
+      <c r="P80" t="s">
+        <v>217</v>
+      </c>
+      <c r="R80" t="s">
         <v>216</v>
-      </c>
-      <c r="P80" t="s">
-        <v>218</v>
-      </c>
-      <c r="R80" t="s">
-        <v>217</v>
       </c>
       <c r="T80" t="s">
         <v>7</v>
@@ -7962,12 +8077,12 @@
         <v>9</v>
       </c>
       <c r="AB80" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="81" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B81" s="5">
         <v>44677</v>
@@ -7979,46 +8094,46 @@
         <v>4.2012790000000004</v>
       </c>
       <c r="E81" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F81" t="s">
         <v>3</v>
       </c>
       <c r="G81" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H81" t="s">
         <v>1</v>
       </c>
       <c r="I81" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J81" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K81" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L81" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M81" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N81" t="s">
         <v>5</v>
       </c>
       <c r="O81" t="s">
+        <v>215</v>
+      </c>
+      <c r="P81" t="s">
+        <v>217</v>
+      </c>
+      <c r="R81" t="s">
         <v>216</v>
       </c>
-      <c r="P81" t="s">
-        <v>218</v>
-      </c>
-      <c r="R81" t="s">
-        <v>217</v>
-      </c>
       <c r="S81" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T81" t="s">
         <v>7</v>
@@ -8033,12 +8148,12 @@
         <v>9</v>
       </c>
       <c r="AB81" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="82" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B82" s="5">
         <v>44677</v>
@@ -8050,46 +8165,46 @@
         <v>4.2011580000000004</v>
       </c>
       <c r="E82" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F82" t="s">
         <v>3</v>
       </c>
       <c r="G82" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H82" t="s">
         <v>1</v>
       </c>
       <c r="I82" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J82" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K82" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L82" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M82" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N82" t="s">
         <v>5</v>
       </c>
       <c r="O82" t="s">
+        <v>215</v>
+      </c>
+      <c r="P82" t="s">
+        <v>217</v>
+      </c>
+      <c r="R82" t="s">
         <v>216</v>
       </c>
-      <c r="P82" t="s">
-        <v>218</v>
-      </c>
-      <c r="R82" t="s">
-        <v>217</v>
-      </c>
       <c r="S82" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T82" t="s">
         <v>7</v>
@@ -8104,12 +8219,12 @@
         <v>9</v>
       </c>
       <c r="AB82" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="83" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B83" s="5">
         <v>44677</v>
@@ -8121,46 +8236,46 @@
         <v>4.2014630000000004</v>
       </c>
       <c r="E83" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F83" t="s">
         <v>3</v>
       </c>
       <c r="G83" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H83" t="s">
         <v>1</v>
       </c>
       <c r="I83" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J83" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K83" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L83" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M83" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N83" t="s">
         <v>5</v>
       </c>
       <c r="O83" t="s">
+        <v>215</v>
+      </c>
+      <c r="P83" t="s">
+        <v>217</v>
+      </c>
+      <c r="R83" t="s">
         <v>216</v>
       </c>
-      <c r="P83" t="s">
-        <v>218</v>
-      </c>
-      <c r="R83" t="s">
-        <v>217</v>
-      </c>
       <c r="S83" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T83" t="s">
         <v>7</v>
@@ -8175,12 +8290,12 @@
         <v>9</v>
       </c>
       <c r="AB83" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="84" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B84" s="5">
         <v>44709</v>
@@ -8192,40 +8307,40 @@
         <v>7.0521060000000002</v>
       </c>
       <c r="E84" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F84" t="s">
         <v>3</v>
       </c>
       <c r="G84" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H84" t="s">
         <v>1</v>
       </c>
       <c r="I84" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J84" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L84" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M84" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N84" t="s">
         <v>5</v>
       </c>
       <c r="O84" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P84" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R84" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T84" t="s">
         <v>7</v>
@@ -8240,12 +8355,12 @@
         <v>9</v>
       </c>
       <c r="AB84" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="85" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B85" s="5">
         <v>44710</v>
@@ -8257,40 +8372,40 @@
         <v>7.036664</v>
       </c>
       <c r="E85" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F85" t="s">
         <v>3</v>
       </c>
       <c r="G85" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H85" t="s">
         <v>1</v>
       </c>
       <c r="I85" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J85" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L85" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M85" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N85" t="s">
         <v>5</v>
       </c>
       <c r="O85" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P85" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R85" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T85" t="s">
         <v>7</v>
@@ -8305,12 +8420,12 @@
         <v>9</v>
       </c>
       <c r="AB85" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="86" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B86" s="5">
         <v>44710</v>
@@ -8322,40 +8437,40 @@
         <v>7.0532690000000002</v>
       </c>
       <c r="E86" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F86" t="s">
         <v>3</v>
       </c>
       <c r="G86" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H86" t="s">
         <v>1</v>
       </c>
       <c r="I86" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J86" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L86" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M86" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N86" t="s">
         <v>5</v>
       </c>
       <c r="O86" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P86" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R86" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T86" t="s">
         <v>7</v>
@@ -8370,12 +8485,12 @@
         <v>9</v>
       </c>
       <c r="AB86" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="87" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B87" s="5">
         <v>44710</v>
@@ -8387,40 +8502,40 @@
         <v>7.0383940000000003</v>
       </c>
       <c r="E87" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F87" t="s">
         <v>3</v>
       </c>
       <c r="G87" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H87" t="s">
         <v>1</v>
       </c>
       <c r="I87" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J87" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L87" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M87" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N87" t="s">
         <v>5</v>
       </c>
       <c r="O87" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P87" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R87" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T87" t="s">
         <v>7</v>
@@ -8435,12 +8550,12 @@
         <v>9</v>
       </c>
       <c r="AB87" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="88" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B88" s="5">
         <v>44817</v>
@@ -8452,46 +8567,46 @@
         <v>0.83678799999999998</v>
       </c>
       <c r="E88" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F88" t="s">
         <v>3</v>
       </c>
       <c r="G88" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H88" t="s">
         <v>1</v>
       </c>
       <c r="I88" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J88" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K88" t="s">
+        <v>361</v>
+      </c>
+      <c r="L88" t="s">
         <v>362</v>
       </c>
-      <c r="L88" t="s">
-        <v>363</v>
-      </c>
       <c r="M88" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N88" t="s">
         <v>5</v>
       </c>
       <c r="O88" t="s">
+        <v>363</v>
+      </c>
+      <c r="P88" t="s">
+        <v>217</v>
+      </c>
+      <c r="R88" t="s">
         <v>364</v>
       </c>
-      <c r="P88" t="s">
-        <v>218</v>
-      </c>
-      <c r="R88" t="s">
-        <v>365</v>
-      </c>
       <c r="S88" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T88" t="s">
         <v>7</v>
@@ -8500,18 +8615,18 @@
         <v>549</v>
       </c>
       <c r="Z88" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA88" t="s">
         <v>9</v>
       </c>
       <c r="AB88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B89" s="5">
         <v>44818</v>
@@ -8523,46 +8638,46 @@
         <v>0.84472199999999997</v>
       </c>
       <c r="E89" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F89" t="s">
         <v>3</v>
       </c>
       <c r="G89" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H89" t="s">
         <v>1</v>
       </c>
       <c r="I89" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="J89" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K89" t="s">
+        <v>361</v>
+      </c>
+      <c r="L89" t="s">
         <v>362</v>
       </c>
-      <c r="L89" t="s">
-        <v>363</v>
-      </c>
       <c r="M89" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N89" t="s">
         <v>5</v>
       </c>
       <c r="O89" t="s">
+        <v>363</v>
+      </c>
+      <c r="P89" t="s">
+        <v>217</v>
+      </c>
+      <c r="R89" t="s">
         <v>364</v>
       </c>
-      <c r="P89" t="s">
-        <v>218</v>
-      </c>
-      <c r="R89" t="s">
-        <v>365</v>
-      </c>
       <c r="S89" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T89" t="s">
         <v>7</v>
@@ -8577,12 +8692,12 @@
         <v>9</v>
       </c>
       <c r="AB89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B90" s="5">
         <v>44839</v>
@@ -8594,46 +8709,46 @@
         <v>13.962123999999999</v>
       </c>
       <c r="E90" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F90" t="s">
         <v>3</v>
       </c>
       <c r="G90" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H90" t="s">
         <v>1</v>
       </c>
       <c r="I90" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="J90" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K90" t="s">
+        <v>372</v>
+      </c>
+      <c r="L90" t="s">
         <v>373</v>
       </c>
-      <c r="L90" t="s">
-        <v>374</v>
-      </c>
       <c r="M90" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N90" t="s">
         <v>5</v>
       </c>
       <c r="O90" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P90" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R90" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S90" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="T90" t="s">
         <v>7</v>
@@ -8648,12 +8763,12 @@
         <v>9</v>
       </c>
       <c r="AB90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B91" s="5">
         <v>44839</v>
@@ -8665,46 +8780,46 @@
         <v>13.963253999999999</v>
       </c>
       <c r="E91" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F91" t="s">
         <v>3</v>
       </c>
       <c r="G91" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H91" t="s">
         <v>1</v>
       </c>
       <c r="I91" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="J91" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K91" t="s">
+        <v>372</v>
+      </c>
+      <c r="L91" t="s">
         <v>373</v>
       </c>
-      <c r="L91" t="s">
-        <v>374</v>
-      </c>
       <c r="M91" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N91" t="s">
         <v>5</v>
       </c>
       <c r="O91" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P91" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R91" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S91" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="T91" t="s">
         <v>7</v>
@@ -8719,12 +8834,12 @@
         <v>9</v>
       </c>
       <c r="AB91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B92" s="5">
         <v>44839</v>
@@ -8736,46 +8851,46 @@
         <v>13.957585</v>
       </c>
       <c r="E92" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F92" t="s">
         <v>3</v>
       </c>
       <c r="G92" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H92" t="s">
         <v>1</v>
       </c>
       <c r="I92" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="J92" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K92" t="s">
+        <v>372</v>
+      </c>
+      <c r="L92" t="s">
         <v>373</v>
       </c>
-      <c r="L92" t="s">
-        <v>374</v>
-      </c>
       <c r="M92" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N92" t="s">
         <v>5</v>
       </c>
       <c r="O92" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P92" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R92" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S92" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="T92" t="s">
         <v>7</v>
@@ -8790,12 +8905,12 @@
         <v>9</v>
       </c>
       <c r="AB92" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="93" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B93" s="5">
         <v>44845</v>
@@ -8807,46 +8922,46 @@
         <v>4.1029470000000003</v>
       </c>
       <c r="E93" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F93" t="s">
         <v>3</v>
       </c>
       <c r="G93" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H93" t="s">
         <v>1</v>
       </c>
       <c r="I93" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J93" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K93" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L93" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="M93" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N93" t="s">
         <v>5</v>
       </c>
       <c r="O93" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P93" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R93" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S93" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T93" t="s">
         <v>7</v>
@@ -8861,12 +8976,12 @@
         <v>9</v>
       </c>
       <c r="AB93" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="94" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B94" s="5">
         <v>44847</v>
@@ -8878,46 +8993,46 @@
         <v>4.2011399999999997</v>
       </c>
       <c r="E94" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F94" t="s">
         <v>3</v>
       </c>
       <c r="G94" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H94" t="s">
         <v>1</v>
       </c>
       <c r="I94" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J94" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K94" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L94" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="M94" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N94" t="s">
         <v>5</v>
       </c>
       <c r="O94" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P94" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R94" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S94" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T94" t="s">
         <v>7</v>
@@ -8932,12 +9047,12 @@
         <v>9</v>
       </c>
       <c r="AB94" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="95" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B95" s="5">
         <v>44860</v>
@@ -8949,46 +9064,46 @@
         <v>0.84643699999999999</v>
       </c>
       <c r="E95" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F95" t="s">
         <v>3</v>
       </c>
       <c r="G95" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H95" t="s">
         <v>1</v>
       </c>
       <c r="I95" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="J95" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K95" t="s">
+        <v>361</v>
+      </c>
+      <c r="L95" t="s">
         <v>362</v>
       </c>
-      <c r="L95" t="s">
-        <v>363</v>
-      </c>
       <c r="M95" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N95" t="s">
         <v>5</v>
       </c>
       <c r="O95" t="s">
+        <v>363</v>
+      </c>
+      <c r="P95" t="s">
+        <v>217</v>
+      </c>
+      <c r="R95" t="s">
         <v>364</v>
       </c>
-      <c r="P95" t="s">
-        <v>218</v>
-      </c>
-      <c r="R95" t="s">
-        <v>365</v>
-      </c>
       <c r="S95" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T95" t="s">
         <v>7</v>
@@ -8997,18 +9112,18 @@
         <v>741</v>
       </c>
       <c r="Z95" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA95" t="s">
         <v>9</v>
       </c>
       <c r="AB95" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="96" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B96" s="5">
         <v>44860</v>
@@ -9020,46 +9135,46 @@
         <v>0.78760300000000005</v>
       </c>
       <c r="E96" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F96" t="s">
         <v>3</v>
       </c>
       <c r="G96" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H96" t="s">
         <v>1</v>
       </c>
       <c r="I96" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J96" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K96" t="s">
+        <v>361</v>
+      </c>
+      <c r="L96" t="s">
         <v>362</v>
       </c>
-      <c r="L96" t="s">
-        <v>363</v>
-      </c>
       <c r="M96" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N96" t="s">
         <v>5</v>
       </c>
       <c r="O96" t="s">
+        <v>363</v>
+      </c>
+      <c r="P96" t="s">
+        <v>217</v>
+      </c>
+      <c r="R96" t="s">
         <v>364</v>
       </c>
-      <c r="P96" t="s">
-        <v>218</v>
-      </c>
-      <c r="R96" t="s">
-        <v>365</v>
-      </c>
       <c r="S96" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T96" t="s">
         <v>7</v>
@@ -9068,18 +9183,18 @@
         <v>853</v>
       </c>
       <c r="Z96" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA96" t="s">
         <v>9</v>
       </c>
       <c r="AB96" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="97" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B97" s="5">
         <v>44873</v>
@@ -9091,40 +9206,40 @@
         <v>7.0470649999999999</v>
       </c>
       <c r="E97" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F97" t="s">
         <v>3</v>
       </c>
       <c r="G97" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H97" t="s">
         <v>1</v>
       </c>
       <c r="I97" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J97" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L97" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="M97" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N97" t="s">
         <v>5</v>
       </c>
       <c r="O97" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P97" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R97" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T97" t="s">
         <v>7</v>
@@ -9133,18 +9248,18 @@
         <v>458</v>
       </c>
       <c r="Z97" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA97" t="s">
         <v>9</v>
       </c>
       <c r="AB97" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="98" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B98" s="5">
         <v>44873</v>
@@ -9156,40 +9271,40 @@
         <v>7.0484530000000003</v>
       </c>
       <c r="E98" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F98" t="s">
         <v>3</v>
       </c>
       <c r="G98" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H98" t="s">
         <v>1</v>
       </c>
       <c r="I98" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J98" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L98" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="M98" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N98" t="s">
         <v>5</v>
       </c>
       <c r="O98" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P98" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R98" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="T98" t="s">
         <v>7</v>
@@ -9198,18 +9313,18 @@
         <v>847</v>
       </c>
       <c r="Z98" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA98" t="s">
         <v>9</v>
       </c>
       <c r="AB98" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="99" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B99" s="5">
         <v>44873</v>
@@ -9221,40 +9336,40 @@
         <v>7.0468200000000003</v>
       </c>
       <c r="E99" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F99" t="s">
         <v>3</v>
       </c>
       <c r="G99" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H99" t="s">
         <v>1</v>
       </c>
       <c r="I99" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J99" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L99" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="M99" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N99" t="s">
         <v>5</v>
       </c>
       <c r="O99" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P99" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R99" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="T99" t="s">
         <v>7</v>
@@ -9263,18 +9378,18 @@
         <v>1085</v>
       </c>
       <c r="Z99" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA99" t="s">
         <v>9</v>
       </c>
       <c r="AB99" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="100" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B100" s="5">
         <v>44874</v>
@@ -9286,40 +9401,40 @@
         <v>7.054608</v>
       </c>
       <c r="E100" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F100" t="s">
         <v>3</v>
       </c>
       <c r="G100" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H100" t="s">
         <v>1</v>
       </c>
       <c r="I100" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J100" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L100" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="M100" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N100" t="s">
         <v>5</v>
       </c>
       <c r="O100" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P100" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R100" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T100" t="s">
         <v>7</v>
@@ -9331,15 +9446,15 @@
         <v>9</v>
       </c>
       <c r="AA100" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AB100" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="101" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B101" s="5">
         <v>44874</v>
@@ -9351,40 +9466,40 @@
         <v>7.0578190000000003</v>
       </c>
       <c r="E101" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F101" t="s">
         <v>3</v>
       </c>
       <c r="G101" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H101" t="s">
         <v>1</v>
       </c>
       <c r="I101" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J101" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L101" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="M101" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N101" t="s">
         <v>5</v>
       </c>
       <c r="O101" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P101" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R101" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T101" t="s">
         <v>7</v>
@@ -9393,18 +9508,18 @@
         <v>948</v>
       </c>
       <c r="Z101" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA101" t="s">
         <v>9</v>
       </c>
       <c r="AB101" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="102" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B102" s="5">
         <v>44874</v>
@@ -9416,40 +9531,40 @@
         <v>7.0403830000000003</v>
       </c>
       <c r="E102" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F102" t="s">
         <v>3</v>
       </c>
       <c r="G102" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H102" t="s">
         <v>1</v>
       </c>
       <c r="I102" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J102" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L102" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="M102" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N102" t="s">
         <v>5</v>
       </c>
       <c r="O102" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P102" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R102" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T102" t="s">
         <v>7</v>
@@ -9458,18 +9573,18 @@
         <v>236</v>
       </c>
       <c r="Z102" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA102" t="s">
         <v>9</v>
       </c>
       <c r="AB102" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="103" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B103" s="5">
         <v>44875</v>
@@ -9481,40 +9596,40 @@
         <v>7.0399839999999996</v>
       </c>
       <c r="E103" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F103" t="s">
         <v>3</v>
       </c>
       <c r="G103" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H103" t="s">
         <v>1</v>
       </c>
       <c r="I103" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J103" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L103" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="M103" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N103" t="s">
         <v>5</v>
       </c>
       <c r="O103" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P103" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R103" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T103" t="s">
         <v>7</v>
@@ -9523,18 +9638,18 @@
         <v>208</v>
       </c>
       <c r="Z103" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA103" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AB103" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="104" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B104" s="5">
         <v>44878</v>
@@ -9546,46 +9661,46 @@
         <v>2.8171300000000001</v>
       </c>
       <c r="E104" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F104" t="s">
         <v>3</v>
       </c>
       <c r="G104" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H104" t="s">
         <v>1</v>
       </c>
       <c r="I104" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J104" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K104" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L104" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M104" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N104" t="s">
         <v>5</v>
       </c>
       <c r="O104" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P104" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R104" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="S104" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="T104" t="s">
         <v>7</v>
@@ -9594,18 +9709,18 @@
         <v>662</v>
       </c>
       <c r="Z104" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA104" t="s">
         <v>9</v>
       </c>
       <c r="AB104" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="105" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B105" s="5">
         <v>44884</v>
@@ -9617,46 +9732,46 @@
         <v>2.8047810000000002</v>
       </c>
       <c r="E105" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F105" t="s">
         <v>3</v>
       </c>
       <c r="G105" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H105" t="s">
         <v>1</v>
       </c>
       <c r="I105" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J105" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K105" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L105" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M105" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N105" t="s">
         <v>5</v>
       </c>
       <c r="O105" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P105" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R105" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="S105" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="T105" t="s">
         <v>7</v>
@@ -9665,18 +9780,18 @@
         <v>386</v>
       </c>
       <c r="Z105" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA105" t="s">
         <v>9</v>
       </c>
       <c r="AB105" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="106" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B106" s="5">
         <v>44885</v>
@@ -9688,46 +9803,46 @@
         <v>2.80782</v>
       </c>
       <c r="E106" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F106" t="s">
         <v>3</v>
       </c>
       <c r="G106" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H106" t="s">
         <v>1</v>
       </c>
       <c r="I106" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J106" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K106" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L106" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M106" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N106" t="s">
         <v>5</v>
       </c>
       <c r="O106" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P106" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R106" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="S106" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="T106" t="s">
         <v>7</v>
@@ -9736,18 +9851,18 @@
         <v>860</v>
       </c>
       <c r="Z106" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA106" t="s">
         <v>9</v>
       </c>
       <c r="AB106" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="107" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B107" s="5">
         <v>44891</v>
@@ -9759,46 +9874,46 @@
         <v>2.7920120000000002</v>
       </c>
       <c r="E107" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F107" t="s">
         <v>3</v>
       </c>
       <c r="G107" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H107" t="s">
         <v>1</v>
       </c>
       <c r="I107" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J107" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K107" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L107" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M107" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N107" t="s">
         <v>5</v>
       </c>
       <c r="O107" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P107" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R107" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="S107" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="T107" t="s">
         <v>7</v>
@@ -9807,18 +9922,18 @@
         <v>422</v>
       </c>
       <c r="Z107" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA107" t="s">
         <v>9</v>
       </c>
       <c r="AB107" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="108" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B108" s="5">
         <v>44894</v>
@@ -9830,46 +9945,46 @@
         <v>2.8015829999999999</v>
       </c>
       <c r="E108" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F108" t="s">
         <v>3</v>
       </c>
       <c r="G108" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H108" t="s">
         <v>1</v>
       </c>
       <c r="I108" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J108" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K108" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L108" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M108" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N108" t="s">
         <v>5</v>
       </c>
       <c r="O108" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P108" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R108" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="S108" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="T108" t="s">
         <v>7</v>
@@ -9878,18 +9993,18 @@
         <v>433</v>
       </c>
       <c r="Z108" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA108" t="s">
         <v>9</v>
       </c>
       <c r="AB108" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="109" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B109" s="5">
         <v>45587</v>
@@ -9901,46 +10016,46 @@
         <v>9.7780050000000003</v>
       </c>
       <c r="E109" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F109" t="s">
         <v>3</v>
       </c>
       <c r="G109" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H109" t="s">
         <v>1</v>
       </c>
       <c r="I109" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="J109" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K109" t="s">
+        <v>417</v>
+      </c>
+      <c r="L109" t="s">
         <v>418</v>
       </c>
-      <c r="L109" t="s">
-        <v>419</v>
-      </c>
       <c r="M109" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N109" t="s">
         <v>5</v>
       </c>
       <c r="O109" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P109" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R109" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S109" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T109" t="s">
         <v>7</v>
@@ -9955,12 +10070,12 @@
         <v>9</v>
       </c>
       <c r="AB109" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="110" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B110" s="5">
         <v>45588</v>
@@ -9972,46 +10087,46 @@
         <v>9.6531310000000001</v>
       </c>
       <c r="E110" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F110" t="s">
         <v>3</v>
       </c>
       <c r="G110" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H110" t="s">
         <v>1</v>
       </c>
       <c r="I110" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="J110" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K110" t="s">
+        <v>417</v>
+      </c>
+      <c r="L110" t="s">
         <v>418</v>
       </c>
-      <c r="L110" t="s">
-        <v>419</v>
-      </c>
       <c r="M110" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N110" t="s">
         <v>5</v>
       </c>
       <c r="O110" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P110" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R110" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S110" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T110" t="s">
         <v>7</v>
@@ -10026,12 +10141,12 @@
         <v>9</v>
       </c>
       <c r="AB110" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="111" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B111" s="5">
         <v>45589</v>
@@ -10043,46 +10158,46 @@
         <v>9.6333769999999994</v>
       </c>
       <c r="E111" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F111" t="s">
         <v>3</v>
       </c>
       <c r="G111" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H111" t="s">
         <v>1</v>
       </c>
       <c r="I111" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="J111" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K111" t="s">
+        <v>417</v>
+      </c>
+      <c r="L111" t="s">
         <v>418</v>
       </c>
-      <c r="L111" t="s">
-        <v>419</v>
-      </c>
       <c r="M111" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N111" t="s">
         <v>5</v>
       </c>
       <c r="O111" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P111" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R111" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S111" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T111" t="s">
         <v>7</v>
@@ -10097,15 +10212,15 @@
         <v>9</v>
       </c>
       <c r="AB111" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="112" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C112" s="6">
         <v>37.184801</v>
@@ -10114,49 +10229,49 @@
         <v>-6.9579510000000004</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J112" s="8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K112" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="L112" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="M112" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="L112" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="M112" s="2" t="s">
-        <v>435</v>
       </c>
       <c r="N112" s="2" t="s">
         <v>5</v>
       </c>
       <c r="O112" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P112" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q112" s="2">
         <v>50</v>
       </c>
       <c r="R112" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="S112" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="T112" s="2" t="s">
         <v>7</v>
@@ -10182,12 +10297,12 @@
       </c>
       <c r="AB112" s="2"/>
     </row>
-    <row r="113" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C113" s="6">
         <v>37.193415999999999</v>
@@ -10196,49 +10311,49 @@
         <v>-6.9629289999999999</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J113" s="8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L113" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N113" s="2" t="s">
         <v>5</v>
       </c>
       <c r="O113" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P113" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q113" s="2">
         <v>50</v>
       </c>
       <c r="R113" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="S113" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="T113" s="2" t="s">
         <v>7</v>
@@ -10264,12 +10379,12 @@
       </c>
       <c r="AB113" s="2"/>
     </row>
-    <row r="114" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C114" s="6">
         <v>37.180356000000003</v>
@@ -10278,49 +10393,49 @@
         <v>-6.9525430000000004</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J114" s="8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="L114" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N114" s="2" t="s">
         <v>5</v>
       </c>
       <c r="O114" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P114" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q114" s="2">
         <v>50</v>
       </c>
       <c r="R114" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="S114" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="T114" s="2" t="s">
         <v>7</v>
@@ -10346,12 +10461,12 @@
       </c>
       <c r="AB114" s="2"/>
     </row>
-    <row r="115" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C115" s="6">
         <v>37.234839000000001</v>
@@ -10360,49 +10475,49 @@
         <v>-6.9618130000000003</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J115" s="8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K115" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="L115" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N115" s="2" t="s">
         <v>5</v>
       </c>
       <c r="O115" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P115" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Q115" s="2">
         <v>50</v>
       </c>
       <c r="R115" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="S115" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="T115" s="2" t="s">
         <v>7</v>
@@ -10428,12 +10543,12 @@
       </c>
       <c r="AB115" s="2"/>
     </row>
-    <row r="116" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C116" s="6">
         <v>37.220008</v>
@@ -10442,49 +10557,49 @@
         <v>-6.9608689999999998</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J116" s="8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L116" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N116" s="2" t="s">
         <v>5</v>
       </c>
       <c r="O116" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P116" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Q116" s="2">
         <v>50</v>
       </c>
       <c r="R116" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="S116" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="T116" s="2" t="s">
         <v>7</v>
@@ -10510,12 +10625,12 @@
       </c>
       <c r="AB116" s="2"/>
     </row>
-    <row r="117" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C117" s="6">
         <v>37.21613</v>
@@ -10524,49 +10639,49 @@
         <v>-6.968572</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J117" s="8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="L117" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N117" s="2" t="s">
         <v>5</v>
       </c>
       <c r="O117" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P117" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Q117" s="2">
         <v>50</v>
       </c>
       <c r="R117" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="S117" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="T117" s="2" t="s">
         <v>7</v>
@@ -10592,12 +10707,12 @@
       </c>
       <c r="AB117" s="2"/>
     </row>
-    <row r="118" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C118" s="6">
         <v>37.210096999999998</v>
@@ -10606,49 +10721,49 @@
         <v>-6.9741730000000004</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J118" s="8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L118" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N118" s="2" t="s">
         <v>5</v>
       </c>
       <c r="O118" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P118" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q118" s="2">
         <v>50</v>
       </c>
       <c r="R118" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="S118" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="T118" s="2" t="s">
         <v>7</v>
@@ -10674,12 +10789,12 @@
       </c>
       <c r="AB118" s="2"/>
     </row>
-    <row r="119" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C119" s="6">
         <v>37.211258999999998</v>
@@ -10688,49 +10803,49 @@
         <v>-6.9582079999999999</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J119" s="8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="L119" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N119" s="2" t="s">
         <v>5</v>
       </c>
       <c r="O119" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P119" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q119" s="2">
         <v>50</v>
       </c>
       <c r="R119" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="S119" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="T119" s="2" t="s">
         <v>7</v>
@@ -10756,12 +10871,12 @@
       </c>
       <c r="AB119" s="2"/>
     </row>
-    <row r="120" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C120" s="6">
         <v>37.151321000000003</v>
@@ -10770,49 +10885,49 @@
         <v>-6.8970539999999998</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J120" s="8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="L120" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N120" s="2" t="s">
         <v>5</v>
       </c>
       <c r="O120" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P120" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q120" s="2">
         <v>50</v>
       </c>
       <c r="R120" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="S120" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="T120" s="2" t="s">
         <v>7</v>
@@ -10838,12 +10953,12 @@
       </c>
       <c r="AB120" s="2"/>
     </row>
-    <row r="121" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C121" s="6">
         <v>37.166437999999999</v>
@@ -10852,49 +10967,49 @@
         <v>-6.9171810000000002</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J121" s="8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L121" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N121" s="2" t="s">
         <v>5</v>
       </c>
       <c r="O121" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P121" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q121" s="2">
         <v>50</v>
       </c>
       <c r="R121" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="S121" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="T121" s="2" t="s">
         <v>7</v>
@@ -10920,12 +11035,12 @@
       </c>
       <c r="AB121" s="2"/>
     </row>
-    <row r="122" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C122" s="6">
         <v>37.202098999999997</v>
@@ -10934,49 +11049,49 @@
         <v>-6.9453329999999998</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J122" s="8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K122" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="L122" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N122" s="2" t="s">
         <v>5</v>
       </c>
       <c r="O122" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P122" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q122" s="2">
         <v>50</v>
       </c>
       <c r="R122" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="S122" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="T122" s="2" t="s">
         <v>7</v>
@@ -11002,28 +11117,602 @@
       </c>
       <c r="AB122" s="2"/>
     </row>
-    <row r="123" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>483</v>
+      </c>
+      <c r="B123" t="s">
+        <v>487</v>
+      </c>
+      <c r="C123">
+        <v>43.457648139089407</v>
+      </c>
+      <c r="D123">
+        <v>-8.2676451455302704</v>
+      </c>
+      <c r="E123" t="s">
+        <v>485</v>
+      </c>
+      <c r="F123" t="s">
+        <v>3</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I123" t="s">
+        <v>484</v>
+      </c>
+      <c r="J123" t="s">
+        <v>125</v>
+      </c>
+      <c r="K123" t="s">
+        <v>488</v>
+      </c>
+      <c r="L123" t="s">
+        <v>489</v>
+      </c>
+      <c r="M123" t="s">
+        <v>126</v>
+      </c>
+      <c r="N123" t="s">
+        <v>486</v>
+      </c>
+      <c r="O123" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P123" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q123">
+        <v>56.8</v>
+      </c>
+      <c r="R123" t="s">
+        <v>247</v>
+      </c>
+      <c r="S123" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="T123" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="U123">
+        <v>1264</v>
+      </c>
+      <c r="V123">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="W123">
+        <v>0.36099999999999999</v>
+      </c>
+      <c r="Y123">
+        <v>1.52</v>
+      </c>
+      <c r="Z123" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA123" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG123" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="124" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>491</v>
+      </c>
+      <c r="B124" t="s">
+        <v>494</v>
+      </c>
+      <c r="C124">
+        <v>43.460978783939161</v>
+      </c>
+      <c r="D124">
+        <v>-8.200915247395141</v>
+      </c>
+      <c r="E124" t="s">
+        <v>493</v>
+      </c>
+      <c r="F124" t="s">
+        <v>3</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I124" t="s">
+        <v>492</v>
+      </c>
+      <c r="J124" t="s">
+        <v>125</v>
+      </c>
+      <c r="K124" t="s">
+        <v>488</v>
+      </c>
+      <c r="L124" t="s">
+        <v>489</v>
+      </c>
+      <c r="M124" t="s">
+        <v>126</v>
+      </c>
+      <c r="N124" t="s">
+        <v>486</v>
+      </c>
+      <c r="O124" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P124" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q124">
+        <v>13.4</v>
+      </c>
+      <c r="R124" t="s">
+        <v>247</v>
+      </c>
+      <c r="S124" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="T124" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="U124">
+        <v>594</v>
+      </c>
+      <c r="V124" s="11" t="s">
+        <v>495</v>
+      </c>
+      <c r="W124">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="Y124">
+        <v>0.35899999999999999</v>
+      </c>
+      <c r="Z124" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA124" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG124" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="125" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>497</v>
+      </c>
+      <c r="B125" t="s">
+        <v>499</v>
+      </c>
+      <c r="C125">
+        <v>43.460743794841541</v>
+      </c>
+      <c r="D125">
+        <v>-8.202317146521068</v>
+      </c>
+      <c r="E125" t="s">
+        <v>498</v>
+      </c>
+      <c r="F125" t="s">
+        <v>3</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I125" t="s">
+        <v>492</v>
+      </c>
+      <c r="J125" t="s">
+        <v>125</v>
+      </c>
+      <c r="K125" t="s">
+        <v>488</v>
+      </c>
+      <c r="L125" t="s">
+        <v>489</v>
+      </c>
+      <c r="M125" t="s">
+        <v>126</v>
+      </c>
+      <c r="N125" t="s">
+        <v>486</v>
+      </c>
+      <c r="O125" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P125" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q125">
+        <v>53.5</v>
+      </c>
+      <c r="R125" t="s">
+        <v>247</v>
+      </c>
+      <c r="S125" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="T125" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="U125">
+        <v>243</v>
+      </c>
+      <c r="V125">
+        <v>7.4499999999999997E-2</v>
+      </c>
+      <c r="W125">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="Y125">
+        <v>1.43</v>
+      </c>
+      <c r="Z125" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA125" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG125" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="126" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>501</v>
+      </c>
+      <c r="B126" t="s">
+        <v>504</v>
+      </c>
+      <c r="C126">
+        <v>43.412464574966883</v>
+      </c>
+      <c r="D126">
+        <v>-8.1658018782165716</v>
+      </c>
+      <c r="E126" t="s">
+        <v>503</v>
+      </c>
+      <c r="F126" t="s">
+        <v>3</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I126" t="s">
+        <v>502</v>
+      </c>
+      <c r="J126" t="s">
+        <v>125</v>
+      </c>
+      <c r="K126" t="s">
+        <v>488</v>
+      </c>
+      <c r="L126" t="s">
+        <v>489</v>
+      </c>
+      <c r="M126" t="s">
+        <v>126</v>
+      </c>
+      <c r="N126" t="s">
+        <v>486</v>
+      </c>
+      <c r="O126" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P126" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q126">
+        <v>25.8</v>
+      </c>
+      <c r="R126" t="s">
+        <v>247</v>
+      </c>
+      <c r="S126" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="T126" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="U126">
+        <v>786</v>
+      </c>
+      <c r="V126">
+        <v>3.7600000000000001E-2</v>
+      </c>
+      <c r="W126">
+        <v>0.371</v>
+      </c>
+      <c r="Y126">
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="Z126" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA126" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG126" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="127" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>506</v>
+      </c>
+      <c r="B127" t="s">
+        <v>509</v>
+      </c>
+      <c r="C127">
+        <v>43.411552465316007</v>
+      </c>
+      <c r="D127">
+        <v>-8.1621295974796197</v>
+      </c>
+      <c r="E127" t="s">
+        <v>508</v>
+      </c>
+      <c r="F127" t="s">
+        <v>3</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I127" t="s">
+        <v>507</v>
+      </c>
+      <c r="J127" t="s">
+        <v>125</v>
+      </c>
+      <c r="K127" t="s">
+        <v>488</v>
+      </c>
+      <c r="L127" t="s">
+        <v>489</v>
+      </c>
+      <c r="M127" t="s">
+        <v>126</v>
+      </c>
+      <c r="N127" t="s">
+        <v>486</v>
+      </c>
+      <c r="O127" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P127" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q127">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="R127" t="s">
+        <v>247</v>
+      </c>
+      <c r="S127" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="T127" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="U127">
+        <v>473</v>
+      </c>
+      <c r="V127">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="W127">
+        <v>0.375</v>
+      </c>
+      <c r="Y127">
+        <v>1.43</v>
+      </c>
+      <c r="Z127" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA127" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG127" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="128" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>511</v>
+      </c>
+      <c r="B128" t="s">
+        <v>514</v>
+      </c>
+      <c r="C128">
+        <v>43.412224634302753</v>
+      </c>
+      <c r="D128">
+        <v>-8.1559919702596453</v>
+      </c>
+      <c r="E128" t="s">
+        <v>513</v>
+      </c>
+      <c r="F128" t="s">
+        <v>3</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I128" t="s">
+        <v>512</v>
+      </c>
+      <c r="J128" t="s">
+        <v>125</v>
+      </c>
+      <c r="K128" t="s">
+        <v>488</v>
+      </c>
+      <c r="L128" t="s">
+        <v>489</v>
+      </c>
+      <c r="M128" t="s">
+        <v>126</v>
+      </c>
+      <c r="N128" t="s">
+        <v>486</v>
+      </c>
+      <c r="O128" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P128" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q128">
+        <v>54.2</v>
+      </c>
+      <c r="R128" t="s">
+        <v>247</v>
+      </c>
+      <c r="S128" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="T128" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="U128">
+        <v>153</v>
+      </c>
+      <c r="V128">
+        <v>5.6800000000000003E-2</v>
+      </c>
+      <c r="W128">
+        <v>0.372</v>
+      </c>
+      <c r="Y128">
+        <v>1.46</v>
+      </c>
+      <c r="Z128" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA128" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG128" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="129" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>516</v>
+      </c>
+      <c r="B129" t="s">
+        <v>519</v>
+      </c>
+      <c r="C129">
+        <v>43.493265880481601</v>
+      </c>
+      <c r="D129">
+        <v>-8.1671022180489423</v>
+      </c>
+      <c r="E129" t="s">
+        <v>518</v>
+      </c>
+      <c r="F129" t="s">
+        <v>3</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I129" t="s">
+        <v>517</v>
+      </c>
+      <c r="J129" t="s">
+        <v>125</v>
+      </c>
+      <c r="K129" t="s">
+        <v>488</v>
+      </c>
+      <c r="L129" t="s">
+        <v>489</v>
+      </c>
+      <c r="M129" t="s">
+        <v>126</v>
+      </c>
+      <c r="N129" t="s">
+        <v>486</v>
+      </c>
+      <c r="O129" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P129" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q129">
+        <v>65.099999999999994</v>
+      </c>
+      <c r="R129" t="s">
+        <v>247</v>
+      </c>
+      <c r="S129" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="T129" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="U129">
+        <v>1945</v>
+      </c>
+      <c r="V129">
+        <v>0.621</v>
+      </c>
+      <c r="W129">
+        <v>0.376</v>
+      </c>
+      <c r="Y129">
+        <v>1.75</v>
+      </c>
+      <c r="Z129" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA129" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG129" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="130" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
